--- a/data/widgets.xlsx
+++ b/data/widgets.xlsx
@@ -10363,7 +10363,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (PDD20/10):</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>p. ej. 0.665</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10699,7 +10699,6 @@
           <t>dosimetria</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>(4, 0, 1, 2)</t>
@@ -15829,7 +15828,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (PDD20/10):</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -15866,7 +15865,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.665</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -16273,7 +16272,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t>Tolerancia (%)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -16855,7 +16854,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (PDD20/10):</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -16892,7 +16891,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.665</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -17299,7 +17298,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t>Tolerancia (%)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -17881,7 +17880,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (J2/J1):</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -17918,7 +17917,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.483</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -18325,7 +18324,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t>Tolerancia (%)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -18907,7 +18906,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (J2/J1):</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -18944,7 +18943,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.483</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -19351,7 +19350,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t>Tolerancia (%)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -19933,7 +19932,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (J2/J1):</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -19970,7 +19969,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.483</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -20959,7 +20958,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (J2/J1):</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20996,7 +20995,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Escribir 1</t>
+          <t>p. ej. 0.483</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21403,7 +21402,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t>Tolerancia (%)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -24600,7 +24599,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Valor teórico (Discrepancia):</t>
+          <t>Calidad de referencia (PDD20/10):</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -24627,7 +24626,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>p. ej. 0.665</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -25412,57 +25411,13 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/widgets.xlsx
+++ b/data/widgets.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="27" activeTab="29" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="encabezado_600" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="preguntas_600" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="btn" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="encabezado_ix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="preguntas_ix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="encabezado_braq" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="preguntas_braq" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="encabezado_mensualBraqui" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="encabezado_ActividadBraqui" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="preguntas_mensualBraqui" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="encabezado_LinealidadBraqui" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="preguntas_LinealidadBraqui" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="preguntas_hal" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="encabezado_mensu_600" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="preguntas_mensu_600" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="encabezado_mensu_IX" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="preguntas_mensu_ix" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="encabezado_mensu_Halcyon" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="preguntas_mensu_Halcyon" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="encabezado_mensu_TAC" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="preguntas_mensu_TAC" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="edit_tabla" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="encabezado_anual_600" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="preguntas_anual_600" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="encabezado_anual_ix" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="preguntas_anual_ix" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="encabezado_anual_Halcyon" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="encabezado_images_ix" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="preguntas_anual_Halcyon" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="encabezado_images_HC" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_600" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_600" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="btn" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_ix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_ix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_braq" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_braq" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_mensualBraqui" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_ActividadBraqui" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_mensualBraqui" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_LinealidadBraqui" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_LinealidadBraqui" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_hal" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_mensu_600" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_mensu_600" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_mensu_IX" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_mensu_ix" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_mensu_Halcyon" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_mensu_Halcyon" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_mensu_TAC" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_mensu_TAC" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="edit_tabla" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_anual_600" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_anual_600" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_anual_ix" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_anual_ix" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_anual_Halcyon" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_images_ix" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="preguntas_anual_Halcyon" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encabezado_images_HC" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IDC-F-RT-126</t>
+          <t>IDC-F-RT-144</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>V.02</t>
+          <t>V.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>                          </t>
+          <t xml:space="preserve">                          </t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>                                                  </t>
+          <t xml:space="preserve">                                                  </t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>                          </t>
+          <t xml:space="preserve">                          </t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>                          </t>
+          <t xml:space="preserve">                          </t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>                          </t>
+          <t xml:space="preserve">                          </t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>                          </t>
+          <t xml:space="preserve">                          </t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>                        </t>
+          <t xml:space="preserve">                        </t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -22664,7 +22664,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7265625" defaultRowHeight="14.5" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="6"/>
@@ -25411,13 +25411,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29051,7 +29044,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>     </t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -29083,7 +29076,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>    </t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -29115,7 +29108,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>    </t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -29147,7 +29140,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>    </t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -29179,7 +29172,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>    </t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -29211,7 +29204,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>    </t>
+          <t xml:space="preserve">    </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -32061,7 +32054,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -33424,7 +33417,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -33456,7 +33449,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -33488,7 +33481,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -33520,7 +33513,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -35547,7 +35540,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -35579,7 +35572,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -35611,7 +35604,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -41805,7 +41798,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IDC-F-RT-126</t>
+          <t>IDC-F-RT-143</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -41837,7 +41830,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>V.02</t>
+          <t>V.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -42036,7 +42029,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IDC-F-RT-126</t>
+          <t>IDC-F-RT-143</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -42068,7 +42061,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>V.02</t>
+          <t>V.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
